--- a/Metrics/SFM_Calibration_crossing.xlsx
+++ b/Metrics/SFM_Calibration_crossing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDAAC50-5F98-4D14-BF04-EF80F394C5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF240559-D71C-44DB-B663-236EF34F9773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Fine tuning:</t>
   </si>
   <si>
-    <t>Stałe:  m=80kg, r=0.2m, v₀=N(1.34,0.26) m/s</t>
-  </si>
-  <si>
     <t>KALIBRACJA SFM - Grid Search na Crossing_90 D_007</t>
   </si>
   <si>
@@ -164,19 +161,7 @@
     <t>Throughput (exit south) [p/s]</t>
   </si>
   <si>
-    <t>kanoniczny (inne r), zator nie pojawia się na środku skrzyżowania jak w ghost tylko w na południowo-wschodnim rogu skrzyżowania; agenci spychają się na niepożądane wyjścia po czym muszą wrócic z powrotem na swój korytarz</t>
-  </si>
-  <si>
-    <t>dochodzi do zderzen między agentami, nie wymijają się tak chętnie, symulacja nie wygląda naturlanie, ten sam zator co powyżej</t>
-  </si>
-  <si>
-    <t>nadal dochodzi do zderzeń i tego samego zatoru, agenci mniej agresywnie zmieniają swoją predkosc</t>
-  </si>
-  <si>
-    <t>trzymanie zauważalnie większych odstępów dzięki czemu nie dochodzi do kolizji, dochodzi jednak nadal do tego samego zatoru lecz nie przy samym rogu - jest to bardziej rozłożone; zostało kilku agentów na koniec którzy wolno wracali do swojego korytarza</t>
-  </si>
-  <si>
-    <t>dochodzi do zderzeń ale nie aż tak mocno jak w cal_01; pojawia się ten sam zator, ageci poruszają się szybciej, na koniec nie zostało wolno poruszających się agentów</t>
+    <t>Stałe:  m=80kg, r=N(0.23,0.01) m, v₀=N(1.34,0.26) m/s</t>
   </si>
 </sst>
 </file>
@@ -207,12 +192,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
@@ -250,7 +237,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,14 +264,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -327,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,6 +361,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,19 +376,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -758,58 +736,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -833,11 +811,11 @@
       <c r="G5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>5</v>
@@ -855,7 +833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -874,33 +852,21 @@
       <c r="F6" s="13">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5">
-        <v>157.82</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2.14</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0.69</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="6">
         <f>0.3*ABS(G6-134.12)/134.12 + 0.125*ABS(H6-2.07)/2.07 + 0.125*ABS(I6-2.44)/2.44 + 0.2*ABS(J6-0.53)/0.53 + 0.25*ABS(K6-0.5)/0.5</f>
-        <v>0.33731892838207678</v>
+        <v>1</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -919,33 +885,21 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8">
-        <v>148.04</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.99</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0.63</v>
-      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="9">
         <f t="shared" ref="L7:L26" si="0">0.3*ABS(G7-134.12)/134.12 + 0.125*ABS(H7-2.07)/2.07 + 0.125*ABS(I7-2.44)/2.44 + 0.2*ABS(J7-0.53)/0.53 + 0.25*ABS(K7-0.5)/0.5</f>
-        <v>0.29187858252378507</v>
+        <v>1</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -964,33 +918,21 @@
       <c r="F8" s="14">
         <v>0.5</v>
       </c>
-      <c r="G8" s="8">
-        <v>148.82</v>
-      </c>
-      <c r="H8" s="8">
-        <v>2.14</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1.93</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0.64</v>
-      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>0.29927284025716372</v>
+        <v>1</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="N8" s="16"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -1009,33 +951,21 @@
       <c r="F9" s="14">
         <v>0.5</v>
       </c>
-      <c r="G9" s="11">
-        <v>158.30000000000001</v>
-      </c>
-      <c r="H9" s="11">
-        <v>2.02</v>
-      </c>
-      <c r="I9" s="11">
-        <v>1.81</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="K9" s="11">
-        <v>0.72</v>
-      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>0.33145527876348851</v>
+        <v>1</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -1054,31 +984,19 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8">
-        <v>150.66</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1.92</v>
-      </c>
-      <c r="I10" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0.65</v>
-      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="9">
         <f t="shared" si="0"/>
-        <v>0.31960479862887686</v>
+        <v>1</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>46</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
@@ -1109,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N11" s="16"/>
     </row>
@@ -1142,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N12" s="16"/>
     </row>
@@ -1175,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N13" s="16"/>
     </row>
@@ -1208,7 +1126,7 @@
         <v>1</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N14" s="16"/>
     </row>
@@ -1241,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N15" s="16"/>
     </row>
@@ -1274,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N16" s="16"/>
     </row>
@@ -1307,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N17" s="16"/>
     </row>
@@ -1340,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -1373,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N19" s="17"/>
     </row>
@@ -1406,42 +1324,42 @@
         <v>1</v>
       </c>
       <c r="M20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N20" s="17"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="20">
+        <v>16</v>
+      </c>
+      <c r="B21" s="21">
+        <v>800</v>
+      </c>
+      <c r="C21" s="21">
+        <v>0.08</v>
+      </c>
+      <c r="D21" s="21">
+        <v>60000</v>
+      </c>
+      <c r="E21" s="21">
+        <v>120000</v>
+      </c>
+      <c r="F21" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="18">
-        <v>16</v>
-      </c>
-      <c r="B21" s="19">
-        <v>800</v>
-      </c>
-      <c r="C21" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="D21" s="19">
-        <v>60000</v>
-      </c>
-      <c r="E21" s="19">
-        <v>120000</v>
-      </c>
-      <c r="F21" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M21" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="23"/>
+      <c r="N21" s="24"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
@@ -1472,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1505,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N23" s="17"/>
     </row>
@@ -1538,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N24" s="17"/>
     </row>
@@ -1571,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -1604,27 +1522,27 @@
         <v>1</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N26" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
@@ -1645,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N32" s="17"/>
     </row>
@@ -1668,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -1691,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N34" s="17"/>
     </row>

--- a/Metrics/SFM_Calibration_crossing.xlsx
+++ b/Metrics/SFM_Calibration_crossing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF240559-D71C-44DB-B663-236EF34F9773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E225B-4646-462E-8C22-342D35D02292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -80,9 +80,6 @@
     <t>KALIBRACJA SFM - Grid Search na Crossing_90 D_007</t>
   </si>
   <si>
-    <t>Cel empiryczny (Ghost D_007_SFM): RSET=134.12s, throughput (exit west)=2.07 ped/s, throughput (exit south)=2.44 ped/s, mean_speed=0.53 m/s, mean_headway=0,50 m</t>
-  </si>
-  <si>
     <t>D_007_SFM</t>
   </si>
   <si>
@@ -161,7 +158,94 @@
     <t>Throughput (exit south) [p/s]</t>
   </si>
   <si>
-    <t>Stałe:  m=80kg, r=N(0.23,0.01) m, v₀=N(1.34,0.26) m/s</t>
+    <t>Stałe:  m=80kg, r=N(0.185,0.015) m, v₀=N(1.34,0.26) m/s</t>
+  </si>
+  <si>
+    <t>Cel empiryczny (Ghost D_007_SFM): RSET=133.69s, throughput (exit west)=2.08 ped/s, throughput (exit south)=2.45 ped/s, mean_speed=0.53 m/s, mean_headway=0,50 m</t>
+  </si>
+  <si>
+    <t>kanoniczny z innym r - dobre wymijanie bez kolizji, zator tworzy się nie na środku (tak jak powinien) tylko na poludniowym zachodzie w rogu miedzy korytarzami, agenci sa wypychani nie na swój korytarz po czym musza wrocic do swojego</t>
+  </si>
+  <si>
+    <t>troche bardzije się od siebie odbijaja, ten sam zator co wyzej ale wiekszy</t>
+  </si>
+  <si>
+    <t>ponownie ten sam zator, agenci nie wchodzą na siebie ale odpychają się na odległość</t>
+  </si>
+  <si>
+    <t>dochodzi do bliższych spotkań między agentami, nie wykrywaja oni siebie na odległoś, chyba większy zator</t>
+  </si>
+  <si>
+    <t>jeszcze bliższe interakcje i kolizje, gorszy wynik wizualnie</t>
+  </si>
+  <si>
+    <t>ten sam efekt co powyżej</t>
+  </si>
+  <si>
+    <t>agenci nadal zbliżają się do siebie (nie aż tak) ale wymijają się w łatwiejszy sposób prześlizgując się między sobą; tworzy się jednak identyczny zator jak w każdym runie powyżej</t>
+  </si>
+  <si>
+    <t>ten sam przypadek jak powyżej lecz większe odbijanie się od siebie spowodowane mniejszym A i brakiem predykcji</t>
+  </si>
+  <si>
+    <t>pominięte - mniejsze A - gorszy wynik</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>sprawniejsze przeciskanie w tłumie, lecz zator tworzy się znowu w tym samym miejscu zamiast na środku skrzyżowania</t>
+  </si>
+  <si>
+    <t>to samo co wyżej lecz bliższe odstępy</t>
+  </si>
+  <si>
+    <t>wcześniejsze wykrywanie innych agentów lecz nadal spychanie na róg gdzie tworzy się zator - i to dosyć duży</t>
+  </si>
+  <si>
+    <t>nadal ten sam problem co wszędzie, sprawniejsze porusznaie się w zatorze</t>
+  </si>
+  <si>
+    <t>lepsze przepuszczanie się w tłumie, zator tworzy isę w rogu ale również trochę na środku</t>
+  </si>
+  <si>
+    <t>podobna sytuacja jak powyżej, szybsze ruchy w tłumie ale zator jest dosyć duży</t>
+  </si>
+  <si>
+    <t>zator jeszcze bardziej przeniósł się na środek co jest pozytywne, w rogu nadal zatrzymują się ludzie</t>
+  </si>
+  <si>
+    <t>poodbna sytuacja jak powyżej ale lepsze przeciskanie się</t>
+  </si>
+  <si>
+    <t>widoczne wpadanie na siebie i duży zator na rogu</t>
+  </si>
+  <si>
+    <t>wpadanie na siebie i odpychanie podobne do symulacji powyżej, taki sam zator w rogu</t>
+  </si>
+  <si>
+    <t>mniejsze wpadanie na siebie</t>
+  </si>
+  <si>
+    <t>utrzymywanie zacznie wiekszych odstepow co spowodowalo glowny zator na srodku, pojedynczy agenci nadal znalezli się w blednych korytarzach</t>
+  </si>
+  <si>
+    <t>D_007_SFM_cal_24</t>
+  </si>
+  <si>
+    <t>D_007_SFM_cal_25</t>
+  </si>
+  <si>
+    <t>D_007_SFM_cal_26</t>
+  </si>
+  <si>
+    <t>niekiedy zauważalne odpychanie między agentami, zator po czesci na srodku jednak grupują się też na rogu w nie tych korytarzach, dochodzi czasem do wpadania na siebie</t>
+  </si>
+  <si>
+    <t>zator przesunięty blizej srodka, w zatorze odległości są nadal za duże</t>
+  </si>
+  <si>
+    <t>podobna sytuacja jak wyżej</t>
   </si>
 </sst>
 </file>
@@ -237,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,6 +350,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -308,7 +404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -364,22 +460,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E41E4-C8F6-4244-B955-9D9C71C2DB24}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
@@ -736,58 +853,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -812,10 +929,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>5</v>
@@ -833,7 +950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -852,26 +969,38 @@
       <c r="F6" s="13">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="7"/>
+      <c r="G6" s="5">
+        <v>146.63999999999999</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1.91</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.67</v>
+      </c>
       <c r="L6" s="6">
-        <f>0.3*ABS(G6-134.12)/134.12 + 0.125*ABS(H6-2.07)/2.07 + 0.125*ABS(I6-2.44)/2.44 + 0.2*ABS(J6-0.53)/0.53 + 0.25*ABS(K6-0.5)/0.5</f>
-        <v>1</v>
+        <f>0.15*ABS(G6-133.69)/133.69 + 0.1*ABS(H6-2.08)/2.08 + 0.1*ABS(I6-2.45)/2.45 + 0.35*ABS(J6-0.53)/0.53 + 0.3*ABS(K6-0.5)/0.5</f>
+        <v>0.39624486434785583</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2</v>
       </c>
       <c r="B7" s="14">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C7" s="14">
         <v>0.08</v>
@@ -885,26 +1014,38 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="G7" s="8">
+        <v>145.69</v>
+      </c>
+      <c r="H7" s="8">
+        <v>2.09</v>
+      </c>
+      <c r="I7" s="8">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0.93</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0.65</v>
+      </c>
       <c r="L7" s="9">
-        <f t="shared" ref="L7:L26" si="0">0.3*ABS(G7-134.12)/134.12 + 0.125*ABS(H7-2.07)/2.07 + 0.125*ABS(I7-2.44)/2.44 + 0.2*ABS(J7-0.53)/0.53 + 0.25*ABS(K7-0.5)/0.5</f>
-        <v>1</v>
+        <f t="shared" ref="L7:L27" si="0">0.15*ABS(G7-133.69)/133.69 + 0.1*ABS(H7-2.08)/2.08 + 0.1*ABS(I7-2.45)/2.45 + 0.35*ABS(J7-0.53)/0.53 + 0.3*ABS(K7-0.5)/0.5</f>
+        <v>0.38360590055184768</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="14">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="C8" s="14">
         <v>0.08</v>
@@ -916,31 +1057,43 @@
         <v>240000</v>
       </c>
       <c r="F8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="8">
+        <v>146.18</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1.98</v>
+      </c>
+      <c r="I8" s="8">
+        <v>2.16</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.97</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0.64</v>
+      </c>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.40522422792090307</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4</v>
       </c>
       <c r="B9" s="14">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="C9" s="14">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="D9" s="14">
         <v>120000</v>
@@ -949,23 +1102,35 @@
         <v>240000</v>
       </c>
       <c r="F9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="11">
+        <v>147.75</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1.91</v>
+      </c>
+      <c r="I9" s="11">
+        <v>2.19</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0.97</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0.64</v>
+      </c>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.40912666062652386</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -984,26 +1149,38 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="G10" s="8">
+        <v>150.69</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1.84</v>
+      </c>
+      <c r="I10" s="8">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1.03</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0.65</v>
+      </c>
       <c r="L10" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.46182152605823734</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="N10" s="16"/>
+        <v>18</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>6</v>
       </c>
       <c r="B11" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="C11" s="14">
         <v>0.08</v>
@@ -1015,122 +1192,170 @@
         <v>240000</v>
       </c>
       <c r="F11" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="8">
+        <v>152.74</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1.83</v>
+      </c>
+      <c r="I11" s="8">
+        <v>2.13</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1.03</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0.62</v>
+      </c>
       <c r="L11" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.44864320885542047</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>7</v>
       </c>
       <c r="B12" s="14">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="C12" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D12" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E12" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F12" s="14">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="G12" s="8">
+        <v>149.65</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1.95</v>
+      </c>
+      <c r="I12" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.97</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0.64</v>
+      </c>
       <c r="L12" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.41300885053304509</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>8</v>
       </c>
       <c r="B13" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C13" s="14">
         <v>0.08</v>
       </c>
       <c r="D13" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E13" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F13" s="14">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="G13" s="8">
+        <v>156.05000000000001</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1.81</v>
+      </c>
+      <c r="I13" s="8">
+        <v>2.08</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.06</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0.65</v>
+      </c>
       <c r="L13" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.49317069994162793</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>9</v>
       </c>
       <c r="B14" s="14">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C14" s="14">
         <v>0.08</v>
       </c>
       <c r="D14" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E14" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F14" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="9" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -1138,172 +1363,232 @@
         <v>1200</v>
       </c>
       <c r="C15" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D15" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="14">
         <v>120000</v>
       </c>
-      <c r="E15" s="14">
-        <v>240000</v>
-      </c>
       <c r="F15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="11">
+        <v>148.47</v>
+      </c>
+      <c r="H15" s="11">
+        <v>1.92</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2.16</v>
+      </c>
+      <c r="J15" s="11">
+        <v>0.97</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0.63</v>
+      </c>
       <c r="L15" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.40467822022226613</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="16"/>
+        <v>23</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>11</v>
       </c>
       <c r="B16" s="14">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="C16" s="14">
         <v>0.08</v>
       </c>
       <c r="D16" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E16" s="14">
         <v>120000</v>
-      </c>
-      <c r="E16" s="14">
-        <v>240000</v>
       </c>
       <c r="F16" s="14">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="G16" s="8">
+        <v>148.65</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.87</v>
+      </c>
+      <c r="I16" s="8">
+        <v>2.21</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.04</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0.65</v>
+      </c>
       <c r="L16" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.46346962490156968</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="16"/>
+        <v>24</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>12</v>
       </c>
       <c r="B17" s="14">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="C17" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D17" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E17" s="14">
         <v>120000</v>
       </c>
-      <c r="E17" s="14">
-        <v>240000</v>
-      </c>
       <c r="F17" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="9" t="e">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="16"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>13</v>
       </c>
-      <c r="B18" s="14">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="20">
+        <v>800</v>
+      </c>
+      <c r="C18" s="20">
         <v>0.12</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="20">
         <v>120000</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="20">
         <v>240000</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="20">
         <v>0.3</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="G18" s="3">
+        <v>148.11000000000001</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.99</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.65</v>
+      </c>
       <c r="L18" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.39554657492870471</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>14</v>
       </c>
       <c r="B19" s="14">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C19" s="14">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="D19" s="14">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E19" s="14">
-        <v>240000</v>
+        <v>160000</v>
       </c>
       <c r="F19" s="14">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="G19" s="3">
+        <v>148.91999999999999</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.66</v>
+      </c>
       <c r="L19" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.41045634167734479</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>15</v>
       </c>
       <c r="B20" s="14">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C20" s="14">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="D20" s="14">
         <v>120000</v>
@@ -1314,311 +1599,596 @@
       <c r="F20" s="14">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
+      <c r="G20" s="11">
+        <v>155.87</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1.83</v>
+      </c>
+      <c r="I20" s="11">
+        <v>2.06</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="K20" s="11">
+        <v>0.7</v>
+      </c>
       <c r="L20" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.45018201881909103</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="20">
+        <v>28</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
         <v>16</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>800</v>
       </c>
-      <c r="C21" s="21">
-        <v>0.08</v>
-      </c>
-      <c r="D21" s="21">
-        <v>60000</v>
-      </c>
-      <c r="E21" s="21">
-        <v>120000</v>
-      </c>
-      <c r="F21" s="21">
+      <c r="C21" s="20">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="20">
+        <v>80000</v>
+      </c>
+      <c r="E21" s="20">
+        <v>160000</v>
+      </c>
+      <c r="F21" s="20">
         <v>0.3</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
+      <c r="G21" s="21">
+        <v>147.31</v>
+      </c>
+      <c r="H21" s="21">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I21" s="21">
+        <v>2.06</v>
+      </c>
+      <c r="J21" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="K21" s="21">
+        <v>0.68</v>
+      </c>
       <c r="L21" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M21" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" s="24"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0.38498191934280995</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>17</v>
       </c>
       <c r="B22" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C22" s="14">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="D22" s="14">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="E22" s="14">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="F22" s="14">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="G22" s="3">
+        <v>147.38999999999999</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.73</v>
+      </c>
       <c r="L22" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.44881660681425739</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>18</v>
       </c>
       <c r="B23" s="14">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="C23" s="14">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="D23" s="14">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="E23" s="14">
-        <v>120000</v>
+        <v>160000</v>
       </c>
       <c r="F23" s="14">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="G23" s="3">
+        <v>145.53</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2.06</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.71</v>
+      </c>
       <c r="L23" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.40547511303231087</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>19</v>
       </c>
       <c r="B24" s="14">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="C24" s="14">
         <v>0.08</v>
       </c>
       <c r="D24" s="14">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="E24" s="14">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="F24" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>148.46</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1.95</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2.13</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.62</v>
+      </c>
       <c r="L24" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.3324114464902842</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>20</v>
       </c>
       <c r="B25" s="14">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="C25" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D25" s="14">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="E25" s="14">
-        <v>120000</v>
+        <v>160000</v>
       </c>
       <c r="F25" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="3">
+        <v>149.87</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.91</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.61</v>
+      </c>
       <c r="L25" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.34271592541944468</v>
       </c>
       <c r="M25" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="26">
+        <v>21</v>
+      </c>
+      <c r="B26" s="27">
+        <v>800</v>
+      </c>
+      <c r="C26" s="27">
+        <v>0.12</v>
+      </c>
+      <c r="D26" s="27">
+        <v>80000</v>
+      </c>
+      <c r="E26" s="27">
+        <v>160000</v>
+      </c>
+      <c r="F26" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="28">
+        <v>147.82</v>
+      </c>
+      <c r="H26" s="28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I26" s="28">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="J26" s="28">
+        <v>0.87</v>
+      </c>
+      <c r="K26" s="28">
+        <v>0.66</v>
+      </c>
+      <c r="L26" s="29">
+        <f t="shared" si="0"/>
+        <v>0.35415098116673588</v>
+      </c>
+      <c r="M26" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>21</v>
-      </c>
-      <c r="B26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="C26" s="14">
+      <c r="N26" s="31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>22</v>
+      </c>
+      <c r="B27" s="14">
+        <v>2000</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60000</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120000</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="3">
+        <v>153.68</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2.02</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="0"/>
+        <v>0.46427370732263384</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+    </row>
+    <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>23</v>
+      </c>
+      <c r="B31" s="14">
+        <v>1200</v>
+      </c>
+      <c r="C31" s="14">
         <v>0.12</v>
       </c>
-      <c r="D26" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E26" s="14">
+      <c r="D31" s="14">
         <v>120000</v>
       </c>
-      <c r="F26" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E31" s="14">
+        <v>240000</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="3">
+        <v>147.75</v>
+      </c>
+      <c r="H31" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="L31" s="9">
+        <f>0.15*ABS(G31-133.69)/133.69 + 0.1*ABS(H31-2.08)/2.08 + 0.1*ABS(I31-2.45)/2.45 + 0.35*ABS(J31-0.53)/0.53 + 0.3*ABS(K31-0.5)/0.5</f>
+        <v>0.39357024938278107</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>22</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="B32" s="14">
+        <v>1200</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120000</v>
+      </c>
+      <c r="E32" s="14">
+        <v>240000</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="3">
+        <v>147.62</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0.74</v>
+      </c>
       <c r="L32" s="9">
-        <f>0.3*ABS(G32-36.3)/36.3 + 0.25*ABS(I32-2.56)/2.56 + 0.2*ABS(J32-0.25)/0.25 + 0.25*ABS(K32-0.34)/0.34</f>
-        <v>1</v>
+        <f t="shared" ref="L32:L35" si="1">0.15*ABS(G32-133.69)/133.69 + 0.1*ABS(H32-2.08)/2.08 + 0.1*ABS(I32-2.45)/2.45 + 0.35*ABS(J32-0.53)/0.53 + 0.3*ABS(K32-0.5)/0.5</f>
+        <v>0.41897972707743614</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="N32" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>23</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="B33" s="14">
+        <v>1200</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120000</v>
+      </c>
+      <c r="E33" s="14">
+        <v>240000</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="3">
+        <v>149.6</v>
+      </c>
+      <c r="H33" s="3">
+        <v>2.13</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1.92</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.86</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0.78</v>
+      </c>
       <c r="L33" s="9">
-        <f t="shared" ref="L33:L34" si="1">0.3*ABS(G33-36.3)/36.3 + 0.25*ABS(I33-2.56)/2.56 + 0.2*ABS(J33-0.25)/0.25 + 0.25*ABS(K33-0.34)/0.34</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.42781202609575908</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N33" s="17"/>
+        <v>64</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>24</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="B34" s="14">
+        <v>2000</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0.12</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120000</v>
+      </c>
+      <c r="E34" s="14">
+        <v>240000</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="3">
+        <v>148.93</v>
+      </c>
+      <c r="H34" s="3">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I34" s="3">
+        <v>1.83</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0.73</v>
+      </c>
       <c r="L34" s="9">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.419229765093874</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N34" s="17"/>
+        <v>65</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>27</v>
+      </c>
+      <c r="B35" s="14">
+        <v>2000</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120000</v>
+      </c>
+      <c r="E35" s="14">
+        <v>240000</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="3">
+        <v>149.09</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1.97</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="L35" s="9">
+        <f t="shared" si="1"/>
+        <v>0.44296422993339535</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A29:N29"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Metrics/SFM_Calibration_crossing.xlsx
+++ b/Metrics/SFM_Calibration_crossing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E225B-4646-462E-8C22-342D35D02292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B65FE3E-5F10-47EE-93BE-0891F7C56A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -77,81 +77,6 @@
     <t>Fine tuning:</t>
   </si>
   <si>
-    <t>KALIBRACJA SFM - Grid Search na Crossing_90 D_007</t>
-  </si>
-  <si>
-    <t>D_007_SFM</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_01</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_02</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_03</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_04</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_05</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_06</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_07</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_08</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_09</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_10</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_11</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_12</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_13</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_14</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_15</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_16</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_17</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_18</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_19</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_20</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_21</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_22</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_23</t>
-  </si>
-  <si>
     <t>Throughput (exit west) [p/s]</t>
   </si>
   <si>
@@ -161,9 +86,6 @@
     <t>Stałe:  m=80kg, r=N(0.185,0.015) m, v₀=N(1.34,0.26) m/s</t>
   </si>
   <si>
-    <t>Cel empiryczny (Ghost D_007_SFM): RSET=133.69s, throughput (exit west)=2.08 ped/s, throughput (exit south)=2.45 ped/s, mean_speed=0.53 m/s, mean_headway=0,50 m</t>
-  </si>
-  <si>
     <t>kanoniczny z innym r - dobre wymijanie bez kolizji, zator tworzy się nie na środku (tak jak powinien) tylko na poludniowym zachodzie w rogu miedzy korytarzami, agenci sa wypychani nie na swój korytarz po czym musza wrocic do swojego</t>
   </si>
   <si>
@@ -188,12 +110,6 @@
     <t>ten sam przypadek jak powyżej lecz większe odbijanie się od siebie spowodowane mniejszym A i brakiem predykcji</t>
   </si>
   <si>
-    <t>pominięte - mniejsze A - gorszy wynik</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
     <t>sprawniejsze przeciskanie w tłumie, lecz zator tworzy się znowu w tym samym miejscu zamiast na środku skrzyżowania</t>
   </si>
   <si>
@@ -230,15 +146,6 @@
     <t>utrzymywanie zacznie wiekszych odstepow co spowodowalo glowny zator na srodku, pojedynczy agenci nadal znalezli się w blednych korytarzach</t>
   </si>
   <si>
-    <t>D_007_SFM_cal_24</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_25</t>
-  </si>
-  <si>
-    <t>D_007_SFM_cal_26</t>
-  </si>
-  <si>
     <t>niekiedy zauważalne odpychanie między agentami, zator po czesci na srodku jednak grupują się też na rogu w nie tych korytarzach, dochodzi czasem do wpadania na siebie</t>
   </si>
   <si>
@@ -246,6 +153,99 @@
   </si>
   <si>
     <t>podobna sytuacja jak wyżej</t>
+  </si>
+  <si>
+    <t>mniejsze odległości między agentami, sprawneijsza ewakuacja -agenci nie stoją w korku jak w danych empirycznych</t>
+  </si>
+  <si>
+    <t>mniejsze odstępy, większy zator w rogu</t>
+  </si>
+  <si>
+    <t>KALIBRACJA SFM - Grid Search na Crossing_90 D_003</t>
+  </si>
+  <si>
+    <t>D_003_SFM</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_01</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_02</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_03</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_04</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_05</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_06</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_07</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_08</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_09</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_10</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_11</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_12</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_13</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_14</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_15</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_16</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_17</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_18</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_19</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_20</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_21</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_22</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_23</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_24</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_25</t>
+  </si>
+  <si>
+    <t>D_003_SFM_cal_26</t>
+  </si>
+  <si>
+    <t>Cel empiryczny (Ghost D_003_SFM): RSET=184s, throughput (exit west)=1.52 ped/s, throughput (exit south)=1.79 ped/s, mean_speed=1.02 m/s, mean_headway=0,61 m</t>
   </si>
 </sst>
 </file>
@@ -321,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,12 +356,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -404,7 +398,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,29 +469,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -853,58 +844,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="A1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
+      <c r="A2" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
+      <c r="A3" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -929,10 +920,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>5</v>
@@ -950,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -969,30 +960,20 @@
       <c r="F6" s="13">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5">
-        <v>146.63999999999999</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1.91</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0.67</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="6">
-        <f>0.15*ABS(G6-133.69)/133.69 + 0.1*ABS(H6-2.08)/2.08 + 0.1*ABS(I6-2.45)/2.45 + 0.35*ABS(J6-0.53)/0.53 + 0.3*ABS(K6-0.5)/0.5</f>
-        <v>0.39624486434785583</v>
+        <f>0.15*ABS(G6-184)/184 + 0.1*ABS(H6-1.52)/1.52 + 0.1*ABS(I6-1.79)/1.79 + 0.35*ABS(J6-1.02)/1.02 + 0.3*ABS(K6-0.61)/0.61</f>
+        <v>1</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1014,30 +995,20 @@
       <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8">
-        <v>145.69</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.93</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0.65</v>
-      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="9">
-        <f t="shared" ref="L7:L27" si="0">0.15*ABS(G7-133.69)/133.69 + 0.1*ABS(H7-2.08)/2.08 + 0.1*ABS(I7-2.45)/2.45 + 0.35*ABS(J7-0.53)/0.53 + 0.3*ABS(K7-0.5)/0.5</f>
-        <v>0.38360590055184768</v>
+        <f t="shared" ref="L7:L27" si="0">0.15*ABS(G7-184)/184 + 0.1*ABS(H7-1.52)/1.52 + 0.1*ABS(I7-1.79)/1.79 + 0.35*ABS(J7-1.02)/1.02 + 0.3*ABS(K7-0.61)/0.61</f>
+        <v>1</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1059,30 +1030,20 @@
       <c r="F8" s="14">
         <v>0.3</v>
       </c>
-      <c r="G8" s="8">
-        <v>146.18</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1.98</v>
-      </c>
-      <c r="I8" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0.64</v>
-      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>0.40522422792090307</v>
+        <v>1</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1104,30 +1065,20 @@
       <c r="F9" s="14">
         <v>0.3</v>
       </c>
-      <c r="G9" s="11">
-        <v>147.75</v>
-      </c>
-      <c r="H9" s="11">
-        <v>1.91</v>
-      </c>
-      <c r="I9" s="11">
-        <v>2.19</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0.97</v>
-      </c>
-      <c r="K9" s="11">
-        <v>0.64</v>
-      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>0.40912666062652386</v>
+        <v>1</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1149,30 +1100,20 @@
       <c r="F10" s="14">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8">
-        <v>150.69</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1.84</v>
-      </c>
-      <c r="I10" s="8">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1.03</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0.65</v>
-      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="9">
         <f t="shared" si="0"/>
-        <v>0.46182152605823734</v>
+        <v>1</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1194,30 +1135,20 @@
       <c r="F11" s="14">
         <v>0.3</v>
       </c>
-      <c r="G11" s="8">
-        <v>152.74</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1.83</v>
-      </c>
-      <c r="I11" s="8">
-        <v>2.13</v>
-      </c>
-      <c r="J11" s="8">
-        <v>1.03</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0.62</v>
-      </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
       <c r="L11" s="9">
         <f t="shared" si="0"/>
-        <v>0.44864320885542047</v>
+        <v>1</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="N11" s="16" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -1239,30 +1170,20 @@
       <c r="F12" s="14">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8">
-        <v>149.65</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1.95</v>
-      </c>
-      <c r="I12" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0.97</v>
-      </c>
-      <c r="K12" s="8">
-        <v>0.64</v>
-      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
       <c r="L12" s="9">
         <f t="shared" si="0"/>
-        <v>0.41300885053304509</v>
+        <v>1</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1284,33 +1205,23 @@
       <c r="F13" s="14">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8">
-        <v>156.05000000000001</v>
-      </c>
-      <c r="H13" s="8">
-        <v>1.81</v>
-      </c>
-      <c r="I13" s="8">
-        <v>2.08</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1.06</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0.65</v>
-      </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
       <c r="L13" s="9">
         <f t="shared" si="0"/>
-        <v>0.49317069994162793</v>
+        <v>1</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -1329,33 +1240,23 @@
       <c r="F14" s="14">
         <v>0.3</v>
       </c>
-      <c r="G14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="9" t="e">
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -1374,30 +1275,20 @@
       <c r="F15" s="14">
         <v>0.3</v>
       </c>
-      <c r="G15" s="11">
-        <v>148.47</v>
-      </c>
-      <c r="H15" s="11">
-        <v>1.92</v>
-      </c>
-      <c r="I15" s="11">
-        <v>2.16</v>
-      </c>
-      <c r="J15" s="11">
-        <v>0.97</v>
-      </c>
-      <c r="K15" s="11">
-        <v>0.63</v>
-      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
       <c r="L15" s="9">
         <f t="shared" si="0"/>
-        <v>0.40467822022226613</v>
+        <v>1</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1419,30 +1310,20 @@
       <c r="F16" s="14">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8">
-        <v>148.65</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1.87</v>
-      </c>
-      <c r="I16" s="8">
-        <v>2.21</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1.04</v>
-      </c>
-      <c r="K16" s="8">
-        <v>0.65</v>
-      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
       <c r="L16" s="9">
         <f t="shared" si="0"/>
-        <v>0.46346962490156968</v>
+        <v>1</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1464,30 +1345,20 @@
       <c r="F17" s="14">
         <v>0.3</v>
       </c>
-      <c r="G17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17" s="9" t="e">
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1509,30 +1380,20 @@
       <c r="F18" s="20">
         <v>0.3</v>
       </c>
-      <c r="G18" s="3">
-        <v>148.11000000000001</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1.99</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0.65</v>
-      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="9">
         <f t="shared" si="0"/>
-        <v>0.39554657492870471</v>
+        <v>1</v>
       </c>
       <c r="M18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>26</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1554,30 +1415,20 @@
       <c r="F19" s="14">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3">
-        <v>148.91999999999999</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1.91</v>
-      </c>
-      <c r="I19" s="3">
-        <v>2.16</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.66</v>
-      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
       <c r="L19" s="9">
         <f t="shared" si="0"/>
-        <v>0.41045634167734479</v>
+        <v>1</v>
       </c>
       <c r="M19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1599,30 +1450,20 @@
       <c r="F20" s="14">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11">
-        <v>155.87</v>
-      </c>
-      <c r="H20" s="11">
-        <v>1.83</v>
-      </c>
-      <c r="I20" s="11">
-        <v>2.06</v>
-      </c>
-      <c r="J20" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="K20" s="11">
-        <v>0.7</v>
-      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="9">
         <f t="shared" si="0"/>
-        <v>0.45018201881909103</v>
+        <v>1</v>
       </c>
       <c r="M20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1644,30 +1485,20 @@
       <c r="F21" s="20">
         <v>0.3</v>
       </c>
-      <c r="G21" s="21">
-        <v>147.31</v>
-      </c>
-      <c r="H21" s="21">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="I21" s="21">
-        <v>2.06</v>
-      </c>
-      <c r="J21" s="21">
-        <v>0.9</v>
-      </c>
-      <c r="K21" s="21">
-        <v>0.68</v>
-      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="9">
         <f t="shared" si="0"/>
-        <v>0.38498191934280995</v>
+        <v>1</v>
       </c>
       <c r="M21" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="23" t="s">
         <v>29</v>
-      </c>
-      <c r="N21" s="23" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1689,30 +1520,20 @@
       <c r="F22" s="14">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3">
-        <v>147.38999999999999</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2.16</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0.73</v>
-      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="9">
         <f t="shared" si="0"/>
-        <v>0.44881660681425739</v>
+        <v>1</v>
       </c>
       <c r="M22" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
         <v>30</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1734,30 +1555,20 @@
       <c r="F23" s="14">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3">
-        <v>145.53</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2.06</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0.71</v>
-      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
       <c r="L23" s="9">
         <f t="shared" si="0"/>
-        <v>0.40547511303231087</v>
+        <v>1</v>
       </c>
       <c r="M23" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1779,30 +1590,20 @@
       <c r="F24" s="14">
         <v>0.5</v>
       </c>
-      <c r="G24" s="3">
-        <v>148.46</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2.13</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.87</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0.62</v>
-      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
       <c r="L24" s="9">
         <f t="shared" si="0"/>
-        <v>0.3324114464902842</v>
+        <v>1</v>
       </c>
       <c r="M24" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1824,78 +1625,58 @@
       <c r="F25" s="14">
         <v>0.5</v>
       </c>
-      <c r="G25" s="3">
-        <v>149.87</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1.91</v>
-      </c>
-      <c r="I25" s="3">
-        <v>2.14</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0.61</v>
-      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
       <c r="L25" s="9">
         <f t="shared" si="0"/>
-        <v>0.34271592541944468</v>
+        <v>1</v>
       </c>
       <c r="M25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="17" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>21</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>800</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>0.12</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="26">
         <v>80000</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="26">
         <v>160000</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="26">
         <v>0.5</v>
       </c>
-      <c r="G26" s="28">
-        <v>147.82</v>
-      </c>
-      <c r="H26" s="28">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="I26" s="28">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="J26" s="28">
-        <v>0.87</v>
-      </c>
-      <c r="K26" s="28">
-        <v>0.66</v>
-      </c>
-      <c r="L26" s="29">
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="9">
         <f t="shared" si="0"/>
-        <v>0.35415098116673588</v>
-      </c>
-      <c r="M26" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M26" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>22</v>
       </c>
@@ -1914,49 +1695,39 @@
       <c r="F27" s="14">
         <v>0.3</v>
       </c>
-      <c r="G27" s="3">
-        <v>153.68</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2.02</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1.93</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0.8</v>
-      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
       <c r="L27" s="9">
         <f t="shared" si="0"/>
-        <v>0.46427370732263384</v>
+        <v>1</v>
       </c>
       <c r="M27" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N27" s="17" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
     </row>
     <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
@@ -1977,30 +1748,20 @@
       <c r="F31" s="14">
         <v>0.5</v>
       </c>
-      <c r="G31" s="3">
-        <v>147.75</v>
-      </c>
-      <c r="H31" s="3">
-        <v>2.25</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1.85</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0.69</v>
-      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
       <c r="L31" s="9">
-        <f>0.15*ABS(G31-133.69)/133.69 + 0.1*ABS(H31-2.08)/2.08 + 0.1*ABS(I31-2.45)/2.45 + 0.35*ABS(J31-0.53)/0.53 + 0.3*ABS(K31-0.5)/0.5</f>
-        <v>0.39357024938278107</v>
+        <f>0.15*ABS(G31-184)/184 + 0.1*ABS(H31-1.52)/1.52 + 0.1*ABS(I31-1.79)/1.79 + 0.35*ABS(J31-1.02)/1.02 + 0.3*ABS(K31-0.61)/0.61</f>
+        <v>1</v>
       </c>
       <c r="M31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N31" s="17" t="s">
         <v>36</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2022,30 +1783,20 @@
       <c r="F32" s="14">
         <v>0.5</v>
       </c>
-      <c r="G32" s="3">
-        <v>147.62</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0.74</v>
-      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
       <c r="L32" s="9">
-        <f t="shared" ref="L32:L35" si="1">0.15*ABS(G32-133.69)/133.69 + 0.1*ABS(H32-2.08)/2.08 + 0.1*ABS(I32-2.45)/2.45 + 0.35*ABS(J32-0.53)/0.53 + 0.3*ABS(K32-0.5)/0.5</f>
-        <v>0.41897972707743614</v>
+        <f t="shared" ref="L32:L35" si="1">0.15*ABS(G32-184)/184 + 0.1*ABS(H32-1.52)/1.52 + 0.1*ABS(I32-1.79)/1.79 + 0.35*ABS(J32-1.02)/1.02 + 0.3*ABS(K32-0.61)/0.61</f>
+        <v>1</v>
       </c>
       <c r="M32" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2067,30 +1818,20 @@
       <c r="F33" s="14">
         <v>0.5</v>
       </c>
-      <c r="G33" s="3">
-        <v>149.6</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2.13</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1.92</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.86</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0.78</v>
-      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
       <c r="L33" s="9">
         <f t="shared" si="1"/>
-        <v>0.42781202609575908</v>
+        <v>1</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2112,30 +1853,20 @@
       <c r="F34" s="14">
         <v>0.5</v>
       </c>
-      <c r="G34" s="3">
-        <v>148.93</v>
-      </c>
-      <c r="H34" s="3">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I34" s="3">
-        <v>1.83</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0.73</v>
-      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
       <c r="L34" s="9">
         <f t="shared" si="1"/>
-        <v>0.419229765093874</v>
+        <v>1</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2157,30 +1888,20 @@
       <c r="F35" s="14">
         <v>0.5</v>
       </c>
-      <c r="G35" s="3">
-        <v>149.09</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1.97</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0.79</v>
-      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
       <c r="L35" s="9">
         <f t="shared" si="1"/>
-        <v>0.44296422993339535</v>
+        <v>1</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Metrics/SFM_Calibration_crossing.xlsx
+++ b/Metrics/SFM_Calibration_crossing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Piotr\CrowdEvacuation\Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B65FE3E-5F10-47EE-93BE-0891F7C56A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B0D9F5-AAC4-444A-B318-421583FFF43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{E00F018A-51B7-4FBE-B871-94FC33AFF981}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -74,9 +74,6 @@
     <t>κ</t>
   </si>
   <si>
-    <t>Fine tuning:</t>
-  </si>
-  <si>
     <t>Throughput (exit west) [p/s]</t>
   </si>
   <si>
@@ -86,81 +83,9 @@
     <t>Stałe:  m=80kg, r=N(0.185,0.015) m, v₀=N(1.34,0.26) m/s</t>
   </si>
   <si>
-    <t>kanoniczny z innym r - dobre wymijanie bez kolizji, zator tworzy się nie na środku (tak jak powinien) tylko na poludniowym zachodzie w rogu miedzy korytarzami, agenci sa wypychani nie na swój korytarz po czym musza wrocic do swojego</t>
-  </si>
-  <si>
-    <t>troche bardzije się od siebie odbijaja, ten sam zator co wyzej ale wiekszy</t>
-  </si>
-  <si>
-    <t>ponownie ten sam zator, agenci nie wchodzą na siebie ale odpychają się na odległość</t>
-  </si>
-  <si>
-    <t>dochodzi do bliższych spotkań między agentami, nie wykrywaja oni siebie na odległoś, chyba większy zator</t>
-  </si>
-  <si>
-    <t>jeszcze bliższe interakcje i kolizje, gorszy wynik wizualnie</t>
-  </si>
-  <si>
-    <t>ten sam efekt co powyżej</t>
-  </si>
-  <si>
-    <t>agenci nadal zbliżają się do siebie (nie aż tak) ale wymijają się w łatwiejszy sposób prześlizgując się między sobą; tworzy się jednak identyczny zator jak w każdym runie powyżej</t>
-  </si>
-  <si>
     <t>ten sam przypadek jak powyżej lecz większe odbijanie się od siebie spowodowane mniejszym A i brakiem predykcji</t>
   </si>
   <si>
-    <t>sprawniejsze przeciskanie w tłumie, lecz zator tworzy się znowu w tym samym miejscu zamiast na środku skrzyżowania</t>
-  </si>
-  <si>
-    <t>to samo co wyżej lecz bliższe odstępy</t>
-  </si>
-  <si>
-    <t>wcześniejsze wykrywanie innych agentów lecz nadal spychanie na róg gdzie tworzy się zator - i to dosyć duży</t>
-  </si>
-  <si>
-    <t>nadal ten sam problem co wszędzie, sprawniejsze porusznaie się w zatorze</t>
-  </si>
-  <si>
-    <t>lepsze przepuszczanie się w tłumie, zator tworzy isę w rogu ale również trochę na środku</t>
-  </si>
-  <si>
-    <t>podobna sytuacja jak powyżej, szybsze ruchy w tłumie ale zator jest dosyć duży</t>
-  </si>
-  <si>
-    <t>zator jeszcze bardziej przeniósł się na środek co jest pozytywne, w rogu nadal zatrzymują się ludzie</t>
-  </si>
-  <si>
-    <t>poodbna sytuacja jak powyżej ale lepsze przeciskanie się</t>
-  </si>
-  <si>
-    <t>widoczne wpadanie na siebie i duży zator na rogu</t>
-  </si>
-  <si>
-    <t>wpadanie na siebie i odpychanie podobne do symulacji powyżej, taki sam zator w rogu</t>
-  </si>
-  <si>
-    <t>mniejsze wpadanie na siebie</t>
-  </si>
-  <si>
-    <t>utrzymywanie zacznie wiekszych odstepow co spowodowalo glowny zator na srodku, pojedynczy agenci nadal znalezli się w blednych korytarzach</t>
-  </si>
-  <si>
-    <t>niekiedy zauważalne odpychanie między agentami, zator po czesci na srodku jednak grupują się też na rogu w nie tych korytarzach, dochodzi czasem do wpadania na siebie</t>
-  </si>
-  <si>
-    <t>zator przesunięty blizej srodka, w zatorze odległości są nadal za duże</t>
-  </si>
-  <si>
-    <t>podobna sytuacja jak wyżej</t>
-  </si>
-  <si>
-    <t>mniejsze odległości między agentami, sprawneijsza ewakuacja -agenci nie stoją w korku jak w danych empirycznych</t>
-  </si>
-  <si>
-    <t>mniejsze odstępy, większy zator w rogu</t>
-  </si>
-  <si>
     <t>KALIBRACJA SFM - Grid Search na Crossing_90 D_003</t>
   </si>
   <si>
@@ -230,22 +155,70 @@
     <t>D_003_SFM_cal_21</t>
   </si>
   <si>
-    <t>D_003_SFM_cal_22</t>
-  </si>
-  <si>
-    <t>D_003_SFM_cal_23</t>
-  </si>
-  <si>
-    <t>D_003_SFM_cal_24</t>
-  </si>
-  <si>
-    <t>D_003_SFM_cal_25</t>
-  </si>
-  <si>
-    <t>D_003_SFM_cal_26</t>
-  </si>
-  <si>
     <t>Cel empiryczny (Ghost D_003_SFM): RSET=184s, throughput (exit west)=1.52 ped/s, throughput (exit south)=1.79 ped/s, mean_speed=1.02 m/s, mean_headway=0,61 m</t>
+  </si>
+  <si>
+    <t>kanoniczny z innym r - brak przewidywania, agenci spychają się na przeciwległe korytarze, zderzenia ale z zachowaniem dystansu - więc nie dochodzi do realnych kolizji, zator w rogu zamiast na środku - i to duży</t>
+  </si>
+  <si>
+    <t>troche bardzije się od siebie odbijaja, o wiele mniejszy zator niż wyżej</t>
+  </si>
+  <si>
+    <t>agenci podchodzą do siebie bliżej przed zderzeniem, dosyć dobre omijanie lecz zator w rogu i tak się utworzył poprzez to samo przepychanie co w runie 1</t>
+  </si>
+  <si>
+    <t>dochodzi do bliższych spotkań między agentami, nie wykrywaja oni siebie na odległość, brak zatoru</t>
+  </si>
+  <si>
+    <t>dochodzi do bezpośrednich spotkań między agentami, przepychają się, znikomy zator pod koniec</t>
+  </si>
+  <si>
+    <t>ten sam efekt co powyżej, większe kolizje, zatoru brak</t>
+  </si>
+  <si>
+    <t>agenci nadal zbliżają się do siebie (nie aż tak) ale wymijają się w łatwiejszy sposób prześlizgując się między sobą; występują zepchnięcia na zły korytarz</t>
+  </si>
+  <si>
+    <t>ten sam przypadek jak powyżej lecz większe odbijanie się od siebie spowodowane mniejszym A i brakiem predykcji, większy zator</t>
+  </si>
+  <si>
+    <t>sprawniejsze przeciskanie w tłumie, trochę agentów ląduje w rogu jak wyżej, szczególnie pod koniec</t>
+  </si>
+  <si>
+    <t>wcześniejsze wykrywanie innych agentów, rzadkie spychanie na róg, zator znikomy</t>
+  </si>
+  <si>
+    <t>to samo co wyżej lecz bliższe odstępy, bezpośrednie kontakty, zderzenia, brak zatoru</t>
+  </si>
+  <si>
+    <t>to samo co wyżej lecz bliższe odstępy, bezpośrednie kontakty, brak zatoru</t>
+  </si>
+  <si>
+    <t>to samo co wyżej lecz doszło do zatoru na rogu</t>
+  </si>
+  <si>
+    <t>wczesne wykrywanie lecz i tak dochodzi do bezpośrednich kontaktów z powodu niskiej siły odpychania, dochodzi do większego zatoru w rogu</t>
+  </si>
+  <si>
+    <t>podobna sytuacja jak powyżej, szybsze ruchy w tłumie i nie dochodzi do aż tylu bezpośrednich kontaktów, doszło do zatoru w rogu lecz mniejszego</t>
+  </si>
+  <si>
+    <t>większy zator, agenci utrzymują większe odstępy i poruszają się wolniej podczas zderzeń, nie dochodzi do bezpośrednich kontaktów</t>
+  </si>
+  <si>
+    <t>poodbna sytuacja jak powyżej ale lepsze przeciskanie się, nadal dosyć duży zator</t>
+  </si>
+  <si>
+    <t>bliższe odstępy, zauważalnie inna charajkterystyka, zderzenia, czasami spychanie, nie do końca realistycznie przez to że agenci wykrywają innych bardzo późno</t>
+  </si>
+  <si>
+    <t>dochodzi do bezpośrednich kontaktów i wpadania na siebie, tworzy się zator w rogu, na końcu został agent który bardzo powolnie wrócił do swojego koryartrza i opóźnił symulację</t>
+  </si>
+  <si>
+    <t>ta sama sytuacja jak wyżej lecz większe odstępy</t>
+  </si>
+  <si>
+    <t>bliskie spotkania i bezpośrednie kontakty, sprawne wymijanie, zator w rogu</t>
   </si>
 </sst>
 </file>
@@ -321,7 +294,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,12 +310,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -398,7 +365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -424,9 +391,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -454,42 +418,70 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -825,79 +817,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E41E4-C8F6-4244-B955-9D9C71C2DB24}">
-  <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.6640625" customWidth="1"/>
+    <col min="14" max="14" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-    </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+    </row>
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,10 +899,10 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -919,11 +911,11 @@
       <c r="G5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>14</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>5</v>
@@ -941,975 +933,1122 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>2000</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <v>0.08</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>120000</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>240000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="7"/>
+      <c r="G6" s="5">
+        <v>195.76</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1.64</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.62</v>
+      </c>
       <c r="L6" s="6">
-        <f>0.15*ABS(G6-184)/184 + 0.1*ABS(H6-1.52)/1.52 + 0.1*ABS(I6-1.79)/1.79 + 0.35*ABS(J6-1.02)/1.02 + 0.3*ABS(K6-0.61)/0.61</f>
-        <v>1</v>
+        <f>0.3*ABS(G6-184)/184 + 0.125*ABS(H6-1.52)/1.52 + 0.125*ABS(I6-1.79)/1.79 + 0.2*ABS(J6-1.02)/1.02 + 0.25*ABS(K6-0.61)/0.61</f>
+        <v>4.8485266129354748E-2</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>2000</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>0.08</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>120000</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>240000</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>0.3</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="9">
-        <f t="shared" ref="L7:L27" si="0">0.15*ABS(G7-184)/184 + 0.1*ABS(H7-1.52)/1.52 + 0.1*ABS(I7-1.79)/1.79 + 0.35*ABS(J7-1.02)/1.02 + 0.3*ABS(K7-0.61)/0.61</f>
-        <v>1</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G7" s="8">
+        <v>184.72</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1.78</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0.61</v>
+      </c>
+      <c r="L7" s="24">
+        <f t="shared" ref="L7:L27" si="0">0.3*ABS(G7-184)/184 + 0.125*ABS(H7-1.52)/1.52 + 0.125*ABS(I7-1.79)/1.79 + 0.2*ABS(J7-1.02)/1.02 + 0.25*ABS(K7-0.61)/0.61</f>
+        <v>2.6224017251583121E-2</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>1500</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>0.08</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>120000</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>240000</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>0.3</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="9">
+      <c r="G8" s="8">
+        <v>183.26</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L8" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+        <v>3.3109446843598497E-2</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
         <v>4</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="27">
         <v>1200</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="27">
         <v>0.08</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="27">
         <v>120000</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="27">
         <v>240000</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="27">
         <v>0.3</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="9">
+      <c r="G9" s="28">
+        <v>183.96</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.52</v>
+      </c>
+      <c r="I9" s="28">
+        <v>1.78</v>
+      </c>
+      <c r="J9" s="28">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L9" s="29">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>3.480404286013096E-2</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>800</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>0.08</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>120000</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>240000</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <v>0.3</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="9">
+      <c r="G10" s="8">
+        <v>182.88</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L10" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>5.0768031076706445E-2</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>600</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>0.08</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>120000</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>240000</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <v>0.3</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="9">
+      <c r="G11" s="8">
+        <v>182.86</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0.54</v>
+      </c>
+      <c r="L11" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+        <v>5.8820569055547278E-2</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>1200</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <v>0.08</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>80000</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>160000</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <v>0.3</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9">
+      <c r="G12" s="8">
+        <v>182.84</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L12" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>4.45973114702609E-2</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>800</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>0.08</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>80000</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>160000</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <v>0.3</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="9">
+      <c r="G13" s="8">
+        <v>182.48</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L13" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>5.407931332582179E-2</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>600</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <v>0.08</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>80000</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>160000</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>0.3</v>
       </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="9">
+      <c r="G14" s="23">
+        <v>183.68</v>
+      </c>
+      <c r="H14" s="23">
+        <v>1.52</v>
+      </c>
+      <c r="I14" s="23">
+        <v>1.79</v>
+      </c>
+      <c r="J14" s="23">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K14" s="23">
+        <v>0.54</v>
+      </c>
+      <c r="L14" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>5.4700459799030043E-2</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>10</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>1200</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <v>0.08</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>60000</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>120000</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>0.3</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="9">
+      <c r="G15" s="10">
+        <v>183.24</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.53</v>
+      </c>
+      <c r="I15" s="10">
+        <v>1.78</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L15" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>3.8761108638387345E-2</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>11</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>800</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13">
         <v>0.08</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>60000</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>120000</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <v>0.3</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="9">
+      <c r="G16" s="8">
+        <v>183.68</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L16" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>4.4542954173829127E-2</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>12</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>600</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13">
         <v>0.08</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>60000</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>120000</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>0.3</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="9">
+      <c r="G17" s="23">
+        <v>183.1</v>
+      </c>
+      <c r="H17" s="23">
+        <v>1.53</v>
+      </c>
+      <c r="I17" s="23">
+        <v>1.78</v>
+      </c>
+      <c r="J17" s="23">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K17" s="23">
+        <v>0.53</v>
+      </c>
+      <c r="L17" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5.9304380758354314E-2</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>13</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="19">
         <v>800</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="19">
         <v>0.12</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="19">
         <v>120000</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="19">
         <v>240000</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="19">
         <v>0.3</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="9">
+      <c r="G18" s="3">
+        <v>188.04</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1.74</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L18" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>3.5113469796948626E-2</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>14</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>800</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>0.12</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>80000</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>160000</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>0.3</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="9">
+      <c r="G19" s="3">
+        <v>183.84</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1.78</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L19" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>2.6626181694281836E-2</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>15</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <v>800</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <v>0.16</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <v>120000</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <v>240000</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <v>0.3</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="9">
+      <c r="G20" s="10">
+        <v>189.22</v>
+      </c>
+      <c r="H20" s="10">
+        <v>1.49</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1.72</v>
+      </c>
+      <c r="J20" s="10">
+        <v>1.06</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="L20" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="19">
+        <v>3.1906101551177256E-2</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
         <v>16</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <v>800</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <v>0.16</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <v>80000</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>160000</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <v>0.3</v>
       </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="9">
+      <c r="G21" s="20">
+        <v>180.74</v>
+      </c>
+      <c r="H21" s="20">
+        <v>1.54</v>
+      </c>
+      <c r="I21" s="20">
+        <v>1.81</v>
+      </c>
+      <c r="J21" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K21" s="20">
+        <v>0.63</v>
+      </c>
+      <c r="L21" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M21" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="N21" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>3.2239598099381692E-2</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>17</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>800</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>0.2</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <v>120000</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>240000</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <v>0.3</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="9">
+      <c r="G22" s="3">
+        <v>194.16</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="L22" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>5.2083814980778076E-2</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>18</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <v>800</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>0.2</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13">
         <v>80000</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="13">
         <v>160000</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="13">
         <v>0.3</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="9">
+      <c r="G23" s="3">
+        <v>188.82</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.53</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="L23" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>4.8274397514305172E-2</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>19</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="13">
         <v>1200</v>
       </c>
-      <c r="C24" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="D24" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E24" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F24" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="9">
+      <c r="C24" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="D24" s="13">
+        <v>40000</v>
+      </c>
+      <c r="E24" s="13">
+        <v>80000</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>182.3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1.53</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L24" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5.6333575900416821E-2</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <v>800</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>0.08</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="13">
         <v>80000</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="13">
         <v>160000</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <v>0.5</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="9">
+      <c r="G25" s="3">
+        <v>188.14</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1.71</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L25" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+        <v>4.7199462046303819E-2</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="13">
         <v>800</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="13">
         <v>0.12</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="13">
         <v>80000</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="13">
         <v>160000</v>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="13">
         <v>0.5</v>
       </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="9">
+      <c r="G26" s="3">
+        <v>197.04</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1.04</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="L26" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M26" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="N26" s="29" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.174006830145989E-2</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>22</v>
       </c>
-      <c r="B27" s="14">
-        <v>2000</v>
-      </c>
-      <c r="C27" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>60000</v>
-      </c>
-      <c r="E27" s="14">
-        <v>120000</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="B27" s="13">
+        <v>1000</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="D27" s="13">
+        <v>40000</v>
+      </c>
+      <c r="E27" s="13">
+        <v>80000</v>
+      </c>
+      <c r="F27" s="13">
         <v>0.3</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="9">
+      <c r="G27" s="3">
+        <v>183.04</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L27" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-    </row>
-    <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>23</v>
-      </c>
-      <c r="B31" s="14">
-        <v>1200</v>
-      </c>
-      <c r="C31" s="14">
-        <v>0.12</v>
-      </c>
-      <c r="D31" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E31" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F31" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="9">
-        <f>0.15*ABS(G31-184)/184 + 0.1*ABS(H31-1.52)/1.52 + 0.1*ABS(I31-1.79)/1.79 + 0.35*ABS(J31-1.02)/1.02 + 0.3*ABS(K31-0.61)/0.61</f>
-        <v>1</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>24</v>
-      </c>
-      <c r="B32" s="14">
-        <v>1200</v>
-      </c>
-      <c r="C32" s="14">
-        <v>0.16</v>
-      </c>
-      <c r="D32" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E32" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F32" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="9">
-        <f t="shared" ref="L32:L35" si="1">0.15*ABS(G32-184)/184 + 0.1*ABS(H32-1.52)/1.52 + 0.1*ABS(I32-1.79)/1.79 + 0.35*ABS(J32-1.02)/1.02 + 0.3*ABS(K32-0.61)/0.61</f>
-        <v>1</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>25</v>
-      </c>
-      <c r="B33" s="14">
-        <v>1200</v>
-      </c>
-      <c r="C33" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="D33" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E33" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N33" s="17" t="s">
+        <v>3.7743295179796799E-2</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>26</v>
-      </c>
-      <c r="B34" s="14">
-        <v>2000</v>
-      </c>
-      <c r="C34" s="14">
-        <v>0.12</v>
-      </c>
-      <c r="D34" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E34" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F34" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>27</v>
-      </c>
-      <c r="B35" s="14">
-        <v>2000</v>
-      </c>
-      <c r="C35" s="14">
-        <v>0.16</v>
-      </c>
-      <c r="D35" s="14">
-        <v>120000</v>
-      </c>
-      <c r="E35" s="14">
-        <v>240000</v>
-      </c>
-      <c r="F35" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>38</v>
-      </c>
+      <c r="N27" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="37"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="37"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="33"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="37"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="33"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="37"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="33"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="37"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L36" s="41"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L37" s="41"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L38" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A29:N29"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
